--- a/data/processed/positivacao/2022-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24607,7 +24607,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B934" t="inlineStr"/>
@@ -36089,7 +36089,7 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr"/>
@@ -64929,7 +64929,7 @@
     <row r="2486">
       <c r="A2486" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2486" t="inlineStr"/>
@@ -66600,12 +66600,12 @@
       <c r="A2551" t="inlineStr"/>
       <c r="B2551" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 67 cliente(s), não positivou 769 cliente(s) - Total vendido: R$ 77.927,58
-Vendedor 3 - FERNANDA: positivou 90 cliente(s), não positivou 351 cliente(s) - Total vendido: R$ 106.974,51
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 90 cliente(s), não positivou 351 cliente(s) - Total vendido: R$ 106.974,51
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 19 cliente(s), não positivou 440 cliente(s) - Total vendido: R$ 3.026,61
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2551" t="inlineStr"/>
